--- a/data/trans_dic/ProblemasDormirP33b-Edad-trans_dic.xlsx
+++ b/data/trans_dic/ProblemasDormirP33b-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con problemas para dormir a diario</t>
+          <t>Población con problemas para dormir a diario (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,49; 10,44</t>
+          <t>2,36; 10,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,98; 14,72</t>
+          <t>4,55; 13,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,37; 10,21</t>
+          <t>4,23; 10,55</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,75; 10,15</t>
+          <t>4,16; 10,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,48; 12,6</t>
+          <t>5,19; 12,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,7; 10,37</t>
+          <t>5,87; 10,54</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,05; 13,55</t>
+          <t>7,78; 13,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,31; 14,92</t>
+          <t>9,41; 14,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,51; 13,65</t>
+          <t>9,38; 13,46</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,65; 13,03</t>
+          <t>3,99; 13,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,19; 22,27</t>
+          <t>15,48; 21,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,97; 16,61</t>
+          <t>8,32; 16,74</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,29; 18,99</t>
+          <t>13,58; 19,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>24,88; 30,3</t>
+          <t>24,51; 30,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19,66; 23,79</t>
+          <t>19,73; 23,7</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14,95; 21,06</t>
+          <t>14,69; 21,03</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,41; 28,57</t>
+          <t>8,11; 28,98</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,79; 23,91</t>
+          <t>9,8; 23,83</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>22,65; 30,93</t>
+          <t>22,67; 30,75</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>32,33; 39,0</t>
+          <t>32,04; 38,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29,24; 34,4</t>
+          <t>29,69; 35,0</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>9,64; 13,47</t>
+          <t>9,41; 13,51</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>15,21; 20,49</t>
+          <t>15,14; 20,55</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13,47; 16,81</t>
+          <t>13,35; 16,81</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con problemas para dormir a diario</t>
+          <t>Población con problemas para dormir a diario (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9948; 41742</t>
+          <t>9459; 43218</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15603; 46112</t>
+          <t>14246; 42436</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31170; 72821</t>
+          <t>30171; 75214</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15884; 42988</t>
+          <t>17601; 45453</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>28065; 64508</t>
+          <t>26603; 62484</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>53285; 97037</t>
+          <t>54930; 98648</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>43175; 72651</t>
+          <t>41738; 71826</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>55094; 88344</t>
+          <t>55725; 88697</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>107309; 154061</t>
+          <t>105849; 151845</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>32416; 115657</t>
+          <t>35440; 116778</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>115394; 158780</t>
+          <t>110327; 156040</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>127498; 265841</t>
+          <t>133236; 267926</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>74562; 106567</t>
+          <t>76202; 106849</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>136341; 166012</t>
+          <t>134294; 168524</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>218005; 263894</t>
+          <t>218795; 262843</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>55035; 77534</t>
+          <t>54100; 77409</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>45089; 173798</t>
+          <t>49368; 176316</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>95639; 233468</t>
+          <t>95689; 232702</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>64035; 87454</t>
+          <t>64114; 86938</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>137670; 166090</t>
+          <t>136430; 165249</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>207176; 243733</t>
+          <t>210399; 248029</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>333670; 466160</t>
+          <t>325701; 467253</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>564511; 760768</t>
+          <t>562143; 762810</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>966335; 1205571</t>
+          <t>957431; 1205638</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/ProblemasDormirP33b-Edad-trans_dic.xlsx
+++ b/data/trans_dic/ProblemasDormirP33b-Edad-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,36; 10,8</t>
+          <t>2,97; 10,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,55; 13,55</t>
+          <t>5,08; 13,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,23; 10,55</t>
+          <t>4,89; 10,6</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,16; 10,73</t>
+          <t>4,1; 10,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,19; 12,2</t>
+          <t>7,8; 14,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,87; 10,54</t>
+          <t>6,6; 10,99</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,94%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,78; 13,39</t>
+          <t>7,39; 12,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,41; 14,98</t>
+          <t>12,0; 16,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,38; 13,46</t>
+          <t>10,35; 14,03</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>16,1%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,99; 13,15</t>
+          <t>10,11; 15,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,48; 21,89</t>
+          <t>17,48; 22,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,32; 16,74</t>
+          <t>14,33; 17,91</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,7%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,58; 19,04</t>
+          <t>13,09; 18,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>24,51; 30,76</t>
+          <t>24,63; 30,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19,73; 23,7</t>
+          <t>19,7; 23,73</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>23,52%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14,69; 21,03</t>
+          <t>15,36; 21,6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,11; 28,98</t>
+          <t>25,15; 31,25</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,8; 23,83</t>
+          <t>21,45; 25,9</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>32,49%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>22,67; 30,75</t>
+          <t>23,45; 32,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>32,04; 38,81</t>
+          <t>32,74; 39,4</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29,69; 35,0</t>
+          <t>29,89; 35,07</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>17,0%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>9,41; 13,51</t>
+          <t>11,83; 14,2</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>15,14; 20,55</t>
+          <t>19,75; 22,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13,35; 16,81</t>
+          <t>16,13; 17,82</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>22376</t>
+          <t>24914</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>26262</t>
+          <t>32413</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48638</t>
+          <t>57326</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9459; 43218</t>
+          <t>12123; 43900</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14246; 42436</t>
+          <t>18400; 50583</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>30171; 75214</t>
+          <t>37668; 81660</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>28203</t>
+          <t>31522</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>46505</t>
+          <t>52070</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>74707</t>
+          <t>83593</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17601; 45453</t>
+          <t>19545; 50842</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26603; 62484</t>
+          <t>39120; 71101</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>54930; 98648</t>
+          <t>64580; 107518</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>56237</t>
+          <t>60100</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>73374</t>
+          <t>88424</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>129611</t>
+          <t>148524</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>41738; 71826</t>
+          <t>45886; 79428</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>55725; 88697</t>
+          <t>74781; 104460</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>105849; 151845</t>
+          <t>128800; 174486</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>77921</t>
+          <t>86182</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>137468</t>
+          <t>145261</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>215389</t>
+          <t>231444</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>35440; 116778</t>
+          <t>70813; 107913</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>110327; 156040</t>
+          <t>128840; 163038</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>133236; 267926</t>
+          <t>205969; 257512</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>89600</t>
+          <t>95843</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>150677</t>
+          <t>168478</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>240277</t>
+          <t>264321</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>76202; 106849</t>
+          <t>79781; 114271</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>134294; 168524</t>
+          <t>149952; 184990</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>218795; 262843</t>
+          <t>239985; 289048</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>66078</t>
+          <t>74938</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>111957</t>
+          <t>124084</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>178035</t>
+          <t>199021</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>54100; 77409</t>
+          <t>62520; 87947</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>49368; 176316</t>
+          <t>110438; 137250</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>95689; 232702</t>
+          <t>181528; 219194</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>75299</t>
+          <t>84368</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>151052</t>
+          <t>167387</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>226351</t>
+          <t>251754</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>64114; 86938</t>
+          <t>72743; 99258</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>136430; 165249</t>
+          <t>152135; 183059</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>210399; 248029</t>
+          <t>231577; 271701</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>415715</t>
+          <t>457867</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>697294</t>
+          <t>778116</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1113009</t>
+          <t>1235984</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>325701; 467253</t>
+          <t>417781; 501711</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>562143; 762810</t>
+          <t>738160; 822248</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>957431; 1205638</t>
+          <t>1172707; 1295263</t>
         </is>
       </c>
     </row>
